--- a/ramy/excelsheet-prototype/prototype.xlsx
+++ b/ramy/excelsheet-prototype/prototype.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ramyayoub\Desktop\IAAC\Master\Semester-3\DATA ENCODING -- DOCUMENTS\OSMnx\OSMnx-data-scraper\ramy\excelsheet-prototype\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FDE70BEF-9BE4-4143-A560-692FBE29EC39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B7EC191-8DE9-4056-8CBF-DB2B2ABC782D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E4199E47-B8DD-4A36-94BF-8E07597CB68D}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="31">
   <si>
     <t>Identifiers</t>
   </si>
@@ -80,9 +80,6 @@
     <t>Morphological</t>
   </si>
   <si>
-    <t>Street width (m)</t>
-  </si>
-  <si>
     <t>Plot area (m²)</t>
   </si>
   <si>
@@ -114,13 +111,31 @@
   </si>
   <si>
     <t>Median income ($)</t>
+  </si>
+  <si>
+    <t>highway_type</t>
+  </si>
+  <si>
+    <t>lanes</t>
+  </si>
+  <si>
+    <t>residential</t>
+  </si>
+  <si>
+    <t>secondary</t>
+  </si>
+  <si>
+    <t>living_street</t>
+  </si>
+  <si>
+    <t>primary</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -198,6 +213,35 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF00B0F0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FFBBBEBF"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF00B0F0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00B0F0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -227,7 +271,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -280,6 +324,46 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -288,7 +372,7 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -326,6 +410,23 @@
     <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="2" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Accent2" xfId="4" builtinId="33"/>
@@ -664,23 +765,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EC65727-B075-4646-97C7-4F6995BF11BD}">
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:N40"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16.36328125" customWidth="1"/>
     <col min="4" max="4" width="14.6328125" customWidth="1"/>
-    <col min="5" max="5" width="17.453125" customWidth="1"/>
-    <col min="6" max="6" width="12.6328125" customWidth="1"/>
-    <col min="7" max="7" width="13.1796875" customWidth="1"/>
-    <col min="8" max="8" width="12.26953125" customWidth="1"/>
-    <col min="9" max="9" width="12.7265625" customWidth="1"/>
-    <col min="10" max="10" width="11.1796875" customWidth="1"/>
-    <col min="11" max="11" width="15.453125" customWidth="1"/>
-    <col min="12" max="12" width="16.54296875" customWidth="1"/>
-    <col min="13" max="13" width="16.6328125" customWidth="1"/>
+    <col min="5" max="5" width="14.6328125" style="21" customWidth="1"/>
+    <col min="6" max="6" width="17.453125" customWidth="1"/>
+    <col min="7" max="7" width="12.6328125" customWidth="1"/>
+    <col min="8" max="8" width="13.1796875" customWidth="1"/>
+    <col min="9" max="9" width="12.26953125" customWidth="1"/>
+    <col min="10" max="10" width="12.7265625" customWidth="1"/>
+    <col min="11" max="11" width="11.1796875" customWidth="1"/>
+    <col min="12" max="12" width="15.453125" customWidth="1"/>
+    <col min="13" max="13" width="16.54296875" customWidth="1"/>
+    <col min="14" max="14" width="16.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="29" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:14" ht="29" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
@@ -689,25 +791,26 @@
       <c r="D1" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="19"/>
+      <c r="F1" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="H1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11" t="s">
+        <v>15</v>
+      </c>
       <c r="I1" s="11"/>
       <c r="J1" s="11"/>
-      <c r="K1" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="L1" s="11"/>
-      <c r="M1" s="12" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" ht="29.5" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="K1" s="11"/>
+      <c r="L1" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1" s="11"/>
+      <c r="N1" s="12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" ht="29.5" thickTop="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -720,42 +823,45 @@
       <c r="D2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="G2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G2" s="6" t="s">
+      <c r="H2" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="J2" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="K2" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="J2" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="K2" s="7" t="s">
+      <c r="L2" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M2" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="L2" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="M2" s="8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N2" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="10"/>
       <c r="C3" s="10"/>
       <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
+      <c r="E3" s="20"/>
       <c r="F3" s="10"/>
       <c r="G3" s="10"/>
       <c r="H3" s="10"/>
@@ -764,8 +870,9 @@
       <c r="K3" s="10"/>
       <c r="L3" s="10"/>
       <c r="M3" s="10"/>
-    </row>
-    <row r="4" spans="1:13" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="N3" s="10"/>
+    </row>
+    <row r="4" spans="1:14" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -778,35 +885,38 @@
       <c r="D4" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="5">
-        <v>11.4</v>
+      <c r="E4" s="13" t="s">
+        <v>28</v>
       </c>
       <c r="F4" s="5">
+        <v>1</v>
+      </c>
+      <c r="G4" s="5">
         <v>320</v>
       </c>
-      <c r="G4" s="6">
+      <c r="H4" s="6">
         <v>60</v>
       </c>
-      <c r="H4" s="6">
+      <c r="I4" s="6">
         <v>1200</v>
       </c>
-      <c r="I4" s="6">
+      <c r="J4" s="6">
         <v>950</v>
       </c>
-      <c r="J4" s="6">
+      <c r="K4" s="6">
         <v>220</v>
       </c>
-      <c r="K4" s="7">
+      <c r="L4" s="7">
         <v>0.38</v>
       </c>
-      <c r="L4" s="7">
+      <c r="M4" s="7">
         <v>0.61</v>
       </c>
-      <c r="M4" s="9">
+      <c r="N4" s="9">
         <v>74000</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:14" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>2</v>
       </c>
@@ -819,35 +929,38 @@
       <c r="D5" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="5">
-        <v>10.199999999999999</v>
+      <c r="E5" s="13" t="s">
+        <v>28</v>
       </c>
       <c r="F5" s="5">
+        <v>1</v>
+      </c>
+      <c r="G5" s="5">
         <v>280</v>
       </c>
-      <c r="G5" s="6">
+      <c r="H5" s="6">
         <v>45</v>
       </c>
-      <c r="H5" s="6">
+      <c r="I5" s="6">
         <v>1450</v>
       </c>
-      <c r="I5" s="6">
+      <c r="J5" s="6">
         <v>870</v>
       </c>
-      <c r="J5" s="6">
+      <c r="K5" s="6">
         <v>310</v>
       </c>
-      <c r="K5" s="7">
+      <c r="L5" s="7">
         <v>0.42</v>
       </c>
-      <c r="L5" s="7">
+      <c r="M5" s="7">
         <v>0.57999999999999996</v>
       </c>
-      <c r="M5" s="9">
+      <c r="N5" s="9">
         <v>69000</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:14" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>3</v>
       </c>
@@ -860,35 +973,38 @@
       <c r="D6" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="5">
-        <v>9.1</v>
+      <c r="E6" s="13" t="s">
+        <v>30</v>
       </c>
       <c r="F6" s="5">
+        <v>2</v>
+      </c>
+      <c r="G6" s="5">
         <v>190</v>
       </c>
-      <c r="G6" s="6">
+      <c r="H6" s="6">
         <v>30</v>
       </c>
-      <c r="H6" s="6">
+      <c r="I6" s="6">
         <v>1600</v>
       </c>
-      <c r="I6" s="6">
+      <c r="J6" s="6">
         <v>720</v>
       </c>
-      <c r="J6" s="6">
+      <c r="K6" s="6">
         <v>180</v>
       </c>
-      <c r="K6" s="7">
+      <c r="L6" s="7">
         <v>0.45</v>
       </c>
-      <c r="L6" s="7">
+      <c r="M6" s="7">
         <v>0.54</v>
       </c>
-      <c r="M6" s="9">
+      <c r="N6" s="9">
         <v>71000</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:14" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>4</v>
       </c>
@@ -901,42 +1017,45 @@
       <c r="D7" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E7" s="5">
-        <v>12.1</v>
+      <c r="E7" s="13" t="s">
+        <v>27</v>
       </c>
       <c r="F7" s="5">
+        <v>1</v>
+      </c>
+      <c r="G7" s="5">
         <v>260</v>
       </c>
-      <c r="G7" s="6">
+      <c r="H7" s="6">
         <v>35</v>
       </c>
-      <c r="H7" s="6">
+      <c r="I7" s="6">
         <v>980</v>
       </c>
-      <c r="I7" s="6">
+      <c r="J7" s="6">
         <v>1100</v>
       </c>
-      <c r="J7" s="6">
+      <c r="K7" s="6">
         <v>150</v>
       </c>
-      <c r="K7" s="7">
+      <c r="L7" s="7">
         <v>0.28999999999999998</v>
       </c>
-      <c r="L7" s="7">
+      <c r="M7" s="7">
         <v>0.7</v>
       </c>
-      <c r="M7" s="9">
+      <c r="N7" s="9">
         <v>82000</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B8" s="10"/>
       <c r="C8" s="10"/>
       <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
+      <c r="E8" s="20"/>
       <c r="F8" s="10"/>
       <c r="G8" s="10"/>
       <c r="H8" s="10"/>
@@ -945,8 +1064,9 @@
       <c r="K8" s="10"/>
       <c r="L8" s="10"/>
       <c r="M8" s="10"/>
-    </row>
-    <row r="9" spans="1:13" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="N8" s="10"/>
+    </row>
+    <row r="9" spans="1:14" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>5</v>
       </c>
@@ -959,35 +1079,38 @@
       <c r="D9" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E9" s="5">
-        <v>9.8000000000000007</v>
+      <c r="E9" s="13" t="s">
+        <v>30</v>
       </c>
       <c r="F9" s="5">
+        <v>2</v>
+      </c>
+      <c r="G9" s="5">
         <v>210</v>
       </c>
-      <c r="G9" s="6">
+      <c r="H9" s="6">
         <v>90</v>
       </c>
-      <c r="H9" s="6">
+      <c r="I9" s="6">
         <v>310</v>
       </c>
-      <c r="I9" s="6">
+      <c r="J9" s="6">
         <v>640</v>
       </c>
-      <c r="J9" s="6">
+      <c r="K9" s="6">
         <v>480</v>
       </c>
-      <c r="K9" s="7">
+      <c r="L9" s="7">
         <v>0.57999999999999996</v>
       </c>
-      <c r="L9" s="7">
+      <c r="M9" s="7">
         <v>0.44</v>
       </c>
-      <c r="M9" s="9">
+      <c r="N9" s="9">
         <v>61000</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:14" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>6</v>
       </c>
@@ -1000,35 +1123,38 @@
       <c r="D10" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E10" s="5">
-        <v>10.5</v>
+      <c r="E10" s="13" t="s">
+        <v>27</v>
       </c>
       <c r="F10" s="5">
+        <v>3</v>
+      </c>
+      <c r="G10" s="5">
         <v>190</v>
       </c>
-      <c r="G10" s="6">
+      <c r="H10" s="6">
         <v>75</v>
       </c>
-      <c r="H10" s="6">
+      <c r="I10" s="6">
         <v>280</v>
       </c>
-      <c r="I10" s="6">
+      <c r="J10" s="6">
         <v>700</v>
       </c>
-      <c r="J10" s="6">
+      <c r="K10" s="6">
         <v>520</v>
       </c>
-      <c r="K10" s="7">
+      <c r="L10" s="7">
         <v>0.61</v>
       </c>
-      <c r="L10" s="7">
+      <c r="M10" s="7">
         <v>0.41</v>
       </c>
-      <c r="M10" s="9">
+      <c r="N10" s="9">
         <v>58000</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>7</v>
       </c>
@@ -1041,40 +1167,216 @@
       <c r="D11" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E11" s="5">
-        <v>11.8</v>
+      <c r="E11" s="13" t="s">
+        <v>29</v>
       </c>
       <c r="F11" s="5">
+        <v>3</v>
+      </c>
+      <c r="G11" s="5">
         <v>680</v>
       </c>
-      <c r="G11" s="6">
+      <c r="H11" s="6">
         <v>110</v>
       </c>
-      <c r="H11" s="6">
+      <c r="I11" s="6">
         <v>740</v>
       </c>
-      <c r="I11" s="6">
+      <c r="J11" s="6">
         <v>600</v>
       </c>
-      <c r="J11" s="6">
+      <c r="K11" s="6">
         <v>290</v>
       </c>
-      <c r="K11" s="7">
+      <c r="L11" s="7">
         <v>0.37</v>
       </c>
-      <c r="L11" s="7">
+      <c r="M11" s="7">
         <v>0.59</v>
       </c>
-      <c r="M11" s="9">
+      <c r="N11" s="9">
         <v>78000</v>
       </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="H16" s="15"/>
+      <c r="I16" s="16"/>
+      <c r="J16" s="16"/>
+      <c r="K16" s="16"/>
+      <c r="L16" s="17"/>
+    </row>
+    <row r="17" spans="8:12" x14ac:dyDescent="0.35">
+      <c r="H17" s="14"/>
+      <c r="I17" s="14"/>
+      <c r="L17" s="18"/>
+    </row>
+    <row r="18" spans="8:12" x14ac:dyDescent="0.35">
+      <c r="H18" s="14"/>
+      <c r="I18" s="14"/>
+      <c r="J18" s="14"/>
+      <c r="K18" s="14"/>
+      <c r="L18" s="14"/>
+    </row>
+    <row r="19" spans="8:12" x14ac:dyDescent="0.35">
+      <c r="H19" s="14"/>
+      <c r="I19" s="14"/>
+      <c r="J19" s="14"/>
+      <c r="K19" s="14"/>
+      <c r="L19" s="14"/>
+    </row>
+    <row r="20" spans="8:12" x14ac:dyDescent="0.35">
+      <c r="H20" s="14"/>
+      <c r="I20" s="14"/>
+      <c r="J20" s="14"/>
+      <c r="K20" s="14"/>
+      <c r="L20" s="14"/>
+    </row>
+    <row r="21" spans="8:12" x14ac:dyDescent="0.35">
+      <c r="H21" s="14"/>
+      <c r="I21" s="14"/>
+      <c r="J21" s="14"/>
+      <c r="K21" s="14"/>
+      <c r="L21" s="14"/>
+    </row>
+    <row r="22" spans="8:12" x14ac:dyDescent="0.35">
+      <c r="H22" s="14"/>
+      <c r="I22" s="14"/>
+      <c r="J22" s="14"/>
+      <c r="K22" s="14"/>
+      <c r="L22" s="14"/>
+    </row>
+    <row r="23" spans="8:12" x14ac:dyDescent="0.35">
+      <c r="H23" s="14"/>
+      <c r="I23" s="14"/>
+      <c r="J23" s="14"/>
+      <c r="K23" s="14"/>
+      <c r="L23" s="14"/>
+    </row>
+    <row r="24" spans="8:12" x14ac:dyDescent="0.35">
+      <c r="H24" s="14"/>
+      <c r="I24" s="14"/>
+      <c r="J24" s="14"/>
+      <c r="K24" s="14"/>
+      <c r="L24" s="14"/>
+    </row>
+    <row r="25" spans="8:12" x14ac:dyDescent="0.35">
+      <c r="H25" s="14"/>
+      <c r="I25" s="14"/>
+      <c r="J25" s="14"/>
+      <c r="K25" s="14"/>
+      <c r="L25" s="14"/>
+    </row>
+    <row r="26" spans="8:12" x14ac:dyDescent="0.35">
+      <c r="H26" s="14"/>
+      <c r="I26" s="14"/>
+      <c r="J26" s="14"/>
+      <c r="K26" s="14"/>
+      <c r="L26" s="14"/>
+    </row>
+    <row r="27" spans="8:12" x14ac:dyDescent="0.35">
+      <c r="H27" s="14"/>
+      <c r="I27" s="14"/>
+      <c r="J27" s="14"/>
+      <c r="K27" s="14"/>
+      <c r="L27" s="14"/>
+    </row>
+    <row r="28" spans="8:12" x14ac:dyDescent="0.35">
+      <c r="H28" s="14"/>
+      <c r="I28" s="14"/>
+      <c r="J28" s="14"/>
+      <c r="K28" s="14"/>
+      <c r="L28" s="14"/>
+    </row>
+    <row r="29" spans="8:12" x14ac:dyDescent="0.35">
+      <c r="H29" s="14"/>
+      <c r="I29" s="14"/>
+      <c r="J29" s="14"/>
+      <c r="K29" s="14"/>
+      <c r="L29" s="14"/>
+    </row>
+    <row r="30" spans="8:12" x14ac:dyDescent="0.35">
+      <c r="H30" s="14"/>
+      <c r="I30" s="14"/>
+      <c r="J30" s="14"/>
+      <c r="K30" s="14"/>
+      <c r="L30" s="14"/>
+    </row>
+    <row r="31" spans="8:12" x14ac:dyDescent="0.35">
+      <c r="H31" s="14"/>
+      <c r="I31" s="14"/>
+      <c r="J31" s="14"/>
+      <c r="K31" s="14"/>
+      <c r="L31" s="14"/>
+    </row>
+    <row r="32" spans="8:12" x14ac:dyDescent="0.35">
+      <c r="H32" s="14"/>
+      <c r="I32" s="14"/>
+      <c r="J32" s="14"/>
+      <c r="K32" s="14"/>
+      <c r="L32" s="14"/>
+    </row>
+    <row r="33" spans="8:12" x14ac:dyDescent="0.35">
+      <c r="H33" s="14"/>
+      <c r="I33" s="14"/>
+      <c r="J33" s="14"/>
+      <c r="K33" s="14"/>
+      <c r="L33" s="14"/>
+    </row>
+    <row r="34" spans="8:12" x14ac:dyDescent="0.35">
+      <c r="H34" s="14"/>
+      <c r="I34" s="14"/>
+      <c r="J34" s="14"/>
+      <c r="K34" s="14"/>
+      <c r="L34" s="14"/>
+    </row>
+    <row r="35" spans="8:12" x14ac:dyDescent="0.35">
+      <c r="H35" s="14"/>
+      <c r="I35" s="14"/>
+      <c r="J35" s="14"/>
+      <c r="K35" s="14"/>
+      <c r="L35" s="14"/>
+    </row>
+    <row r="36" spans="8:12" x14ac:dyDescent="0.35">
+      <c r="H36" s="14"/>
+      <c r="I36" s="14"/>
+      <c r="J36" s="14"/>
+      <c r="K36" s="14"/>
+      <c r="L36" s="14"/>
+    </row>
+    <row r="37" spans="8:12" x14ac:dyDescent="0.35">
+      <c r="H37" s="14"/>
+      <c r="I37" s="14"/>
+      <c r="J37" s="14"/>
+      <c r="K37" s="14"/>
+      <c r="L37" s="14"/>
+    </row>
+    <row r="38" spans="8:12" x14ac:dyDescent="0.35">
+      <c r="H38" s="14"/>
+      <c r="I38" s="14"/>
+      <c r="J38" s="14"/>
+      <c r="K38" s="14"/>
+      <c r="L38" s="14"/>
+    </row>
+    <row r="39" spans="8:12" x14ac:dyDescent="0.35">
+      <c r="H39" s="14"/>
+      <c r="I39" s="14"/>
+      <c r="J39" s="14"/>
+      <c r="K39" s="14"/>
+      <c r="L39" s="14"/>
+    </row>
+    <row r="40" spans="8:12" x14ac:dyDescent="0.35">
+      <c r="H40" s="14"/>
+      <c r="I40" s="14"/>
+      <c r="J40" s="14"/>
+      <c r="K40" s="14"/>
+      <c r="L40" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A1:C1"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="H1:K1"/>
+    <mergeCell ref="L1:M1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
